--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="472">
   <si>
     <t xml:space="preserve">Rozdělení projektu SI2 – telemedicínský systém</t>
   </si>
@@ -1239,56 +1239,222 @@
     <t xml:space="preserve">Celkem</t>
   </si>
   <si>
-    <t xml:space="preserve">Harmonogram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Typ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co má být hotovo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konzultace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sběr požadavků; výběr choroby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interní milník</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Choroba, požadavky, seznam aktérů, hrubé rozhraní mezi bloky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Component diagram, use case diagramy, návrh DB, stavové diagramy, rozdělení zodpovědnosti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GUI návrhy a průřezové kapitoly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odevzdání</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prezentace výstupu a odevzdání práce (cca 20 stran + 10–15 slidů)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zápočet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrola zapracování připomínek (v zadání uvedeno 7.1.2026, zřejmě překlep)</t>
+    <t xml:space="preserve">Týdenní harmonogram (termín = středa večer, ve čtvrtek se na hodině kontroluje)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Čísla #N odpovídají úkolům v listu Úkoly. Vše hotovo do 9.12., týden 10.–16.12. je rezerva.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Týden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Od</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konzultace / milník</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10. konzultace – sběr požadavků</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#1 vybrat a nahlásit chorobu; #3 aktéři a hrubé schéma; založit GitHub, OneDrive, šablonu diagramů; začít #2 požadavky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasbírat požadavky na aplikaci a senzor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasbírat požadavky na portál a role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasbírat požadavky na API a data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nasbírat požadavky na integrátor; rešerše současných řešení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2 dokončit analýzu požadavků; začít #5 dohodu rozhraní</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Začít #7 UC pacientská aplikace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Začít #13 UC portál</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Začít #18 UC API; sbírat požadavky na data pro DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Začít #23 UC integrátor; nastudovat FHIR (#25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#6 bezpečnost a GDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#7 UC hotovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#13 UC hotovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#18 UC hotovo; první návrh tabulek (#20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#23 UC hotovo; mapování na FHIR zdroje (#25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5 dohoda rozhraní finální; role 3 kreslí návrh component diagramu (#4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#8 + #9 stavové diagramy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#14 stavový diagram alertu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#19 stavový diagram; #20 ER diagram hotový</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#24 stavový diagram synchronizace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propojení: vše zkontrolovat před konzultací</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#4 component diagram finální; všichni si navzájem zkontrolují diagramy (soulad UC ↔ DB ↔ rozhraní)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#10 popis pacientské části</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#15 popis portálu a oprávnění</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#21 popis API a DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#25 popis integrátoru a FHIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.11. konzultace – architektura a rozdělení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapracovat připomínky z konzultace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wireframy mobilní aplikace (#11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wireframy portálu (#16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Začít #22 Implementace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#26 Úvod hotový</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sjednotit vzhled GUI (aplikace × portál)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#11 GUI aplikace hotové; začít #12 Údržba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#16 GUI portálu hotové; začít #17 Testování (sebrat scénáře od ostatních)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#22 Implementace – koncept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Začít #27 Nasazení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.11. konzultace – kontrola postupu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapracovat připomínky; #28 Zhodnocení; osnova prezentace (#30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#12 Údržba hotová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#17 Testování hotové</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#22 Implementace hotová</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#27 Nasazení hotové</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOKONČENO: dokument i prezentace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#31 spojit dokument, kontrola minimálních požadavků, jednotný styl, obsah a zdroje; #30 slidy; #29 výkaz práce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–3 slidy + korektura cizí kapitoly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REZERVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jen opravy a nácvik prezentace (cca 15 min s časomírou), příprava odpovědí na otázky komise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezerva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.12. prezentace a odevzdání</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezentace a obhajoba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1. zápočet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapracovat připomínky komise</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="dd\.mm\."/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1349,7 +1515,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1359,7 +1525,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1371,12 +1537,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
@@ -1430,7 +1608,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1496,6 +1674,42 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1588,7 +1802,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1598,13 +1812,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFC6EFCE"/>
       <rgbColor rgb="FFFFEB9C"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFCE4D6"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -2092,7 +2306,7 @@
         <v>51</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>52</v>
@@ -2117,7 +2331,7 @@
         <v>51</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>52</v>
@@ -2142,7 +2356,7 @@
         <v>51</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>52</v>
@@ -2167,7 +2381,7 @@
         <v>51</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>52</v>
@@ -2192,7 +2406,7 @@
         <v>51</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>52</v>
@@ -2217,7 +2431,7 @@
         <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>52</v>
@@ -2242,7 +2456,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>52</v>
@@ -2267,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>52</v>
@@ -2292,7 +2506,7 @@
         <v>3</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>52</v>
@@ -2317,7 +2531,7 @@
         <v>3</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>52</v>
@@ -2342,7 +2556,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>46352</v>
+        <v>46358</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>52</v>
@@ -2367,7 +2581,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>52</v>
@@ -2392,7 +2606,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>52</v>
@@ -2417,7 +2631,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>52</v>
@@ -2442,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>52</v>
@@ -2467,7 +2681,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>46352</v>
+        <v>46358</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>52</v>
@@ -2492,7 +2706,7 @@
         <v>5</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>52</v>
@@ -2517,7 +2731,7 @@
         <v>5</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>52</v>
@@ -2542,7 +2756,7 @@
         <v>5</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>52</v>
@@ -2567,7 +2781,7 @@
         <v>5</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>52</v>
@@ -2592,7 +2806,7 @@
         <v>5</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>46352</v>
+        <v>46358</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>52</v>
@@ -2617,7 +2831,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>46338</v>
+        <v>46323</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>52</v>
@@ -2642,7 +2856,7 @@
         <v>6</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>46338</v>
+        <v>46330</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>52</v>
@@ -2667,7 +2881,7 @@
         <v>6</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>46338</v>
+        <v>46337</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>52</v>
@@ -2692,7 +2906,7 @@
         <v>6</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>46352</v>
+        <v>46344</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>52</v>
@@ -2717,7 +2931,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>46352</v>
+        <v>46358</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>52</v>
@@ -2742,7 +2956,7 @@
         <v>51</v>
       </c>
       <c r="E32" s="9" t="n">
-        <v>46373</v>
+        <v>46358</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>52</v>
@@ -2767,7 +2981,7 @@
         <v>51</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>46373</v>
+        <v>46365</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>52</v>
@@ -2792,7 +3006,7 @@
         <v>51</v>
       </c>
       <c r="E34" s="9" t="n">
-        <v>46373</v>
+        <v>46365</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>52</v>
@@ -2817,7 +3031,7 @@
         <v>51</v>
       </c>
       <c r="E35" s="9" t="n">
-        <v>46373</v>
+        <v>46365</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>52</v>
@@ -6253,12 +6467,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6266,82 +6483,363 @@
         <v>403</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
+      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="B5" s="18" t="n">
         <v>46303</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
+      <c r="C5" s="19" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>410</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B6" s="21" t="n">
         <v>46310</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+      <c r="C6" s="9" t="n">
+        <v>46316</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B7" s="21" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>46323</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>46324</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>46330</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>46331</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>46337</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
+        <v>440</v>
+      </c>
+      <c r="B10" s="18" t="n">
         <v>46338</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+      <c r="C10" s="19" t="n">
+        <v>46344</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>442</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>444</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>445</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>46345</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>46351</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="B12" s="18" t="n">
         <v>46352</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+      <c r="C12" s="19" t="n">
+        <v>46358</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>455</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>456</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>457</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>458</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>46359</v>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>46365</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>461</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="H13" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>46366</v>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>46372</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>465</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="H14" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="18" t="n">
         <v>46373</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
+      <c r="C15" s="19" t="n">
+        <v>46373</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>469</v>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>46374</v>
+      </c>
+      <c r="C16" s="19" t="n">
         <v>46394</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>416</v>
-      </c>
+      <c r="D16" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Harmonogram" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Osnova kroků'!$A$4:$G$170</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Osnova kroků'!$A$4:$G$171</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Úkoly!$A$4:$H$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -29,9 +29,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="555">
-  <si>
-    <t xml:space="preserve">Rozdělení projektu SI2 – telemedicínský systém pro pacienty s hypertenzí</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="564">
+  <si>
+    <t xml:space="preserve">Rozdělení projektu SI2 – telemedicínský systém pro mladé dospělé (18–40) s hypertenzí – vliv soli a energetických nápojů</t>
   </si>
   <si>
     <t xml:space="preserve">Člen týmu (doplňte jméno):</t>
@@ -55,10 +55,10 @@
     <t xml:space="preserve">Blok systému</t>
   </si>
   <si>
-    <t xml:space="preserve">Tlakoměr s Bluetooth + pacientská aplikace (mobil), sledování fyzické aktivity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Portál pro pacienty a lékaře, role a oprávnění</t>
+    <t xml:space="preserve">Tlakoměr s Bluetooth + pacientská aplikace (mobil), sledování fyzické aktivity, rychlý záznam soli a energetických nápojů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portál pro pacienty a lékaře, role a oprávnění, graf tlak × životospráva</t>
   </si>
   <si>
     <t xml:space="preserve">Zabezpečené API, zpracování dat, autentizace</t>
@@ -199,6 +199,18 @@
     <t xml:space="preserve">Hypertenze, nahlášeno 8.10.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cílová skupina a zaměření</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mladí dospělí 18–40 let; vliv soli a energetických nápojů (ruční rychlý záznam); děti a těhotné vyloučeny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozhodnuto týmem</t>
+  </si>
+  <si>
     <t xml:space="preserve">Termíny</t>
   </si>
   <si>
@@ -274,9 +286,6 @@
     <t xml:space="preserve">Smíme, není třeba uvádět</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
     <t xml:space="preserve">GitHub</t>
   </si>
   <si>
@@ -322,6 +331,18 @@
     <t xml:space="preserve">Odesílání měření do NIS; volitelně načtení údajů pacienta</t>
   </si>
   <si>
+    <t xml:space="preserve">Posílat záznamy životosprávy (sůl, energetické nápoje) do NIS?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Týdenní souhrn jako FHIR Observation (social-history)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je zaměření na mladé a životosprávu v pořádku?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ověřit na konzultaci</t>
+  </si>
+  <si>
     <t xml:space="preserve">Úkoly – sledování postupu</t>
   </si>
   <si>
@@ -532,37 +553,37 @@
     <t xml:space="preserve">2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Sepsat seznam aktérů: pacient, lékař, administrátor, NIS, senzor (případně sestra / rodinný příslušník).</t>
+    <t xml:space="preserve">Cílová skupina: mladí dospělí 18–40 let s léčenou hypertenzí, u nichž hraje roli životní styl (sůl, energetické nápoje, málo pohybu). Vyloučit děti/dospívající a těhotné.</t>
   </si>
   <si>
     <t xml:space="preserve">2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Brainstorming funkčních požadavků po blocích (aplikace, portál, API, integrátor); každý přinese 5–10 požadavků za svůj blok.</t>
+    <t xml:space="preserve">Vytvořit 2–3 persony, např. student 22 let (energetické nápoje při zkouškách), IT pracovník 34 let (sedavá práce, slané jídlo), praktický lékař.</t>
   </si>
   <si>
     <t xml:space="preserve">2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Sepsat nefunkční požadavky: bezpečnost (šifrování, autentizace), dostupnost, výkon, offline režim, GDPR, škálovatelnost, použitelnost pro seniory.</t>
+    <t xml:space="preserve">Brainstorming funkčních požadavků po blocích; každý přinese 5–10 požadavků. Nezapomenout na rychlý záznam soli a energetických nápojů a jeho zobrazení lékaři.</t>
   </si>
   <si>
     <t xml:space="preserve">2.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Očíslovat požadavky (FP-01…, NFP-01…) a přiřadit prioritu (MoSCoW: Must / Should / Could / Won't).</t>
+    <t xml:space="preserve">Nefunkční požadavky: bezpečnost, GDPR, dostupnost, offline režim, rychlost zadání (záznam do 3 klepnutí), motivace k pravidelnému používání.</t>
   </si>
   <si>
     <t xml:space="preserve">2.5</t>
   </si>
   <si>
-    <t xml:space="preserve">Projít s cvičícím na konzultaci a zapracovat připomínky.</t>
+    <t xml:space="preserve">Očíslovat požadavky (FP-01…, NFP-01…) a přiřadit prioritu MoSCoW; záznam životosprávy jako Must, motivační prvky jako Could.</t>
   </si>
   <si>
     <t xml:space="preserve">2.6</t>
   </si>
   <si>
-    <t xml:space="preserve">Sepsat kapitolu „Analýza požadavků“ (tabulka požadavků + krátký úvodní text).</t>
+    <t xml:space="preserve">Projít s cvičícími a sepsat kapitolu „Analýza požadavků“ (tabulka + úvodní text).</t>
   </si>
   <si>
     <t xml:space="preserve">3.1</t>
@@ -694,25 +715,25 @@
     <t xml:space="preserve">7.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Aktéři (min. 2, každý min. 4 use casy): Pacient, Tlakoměr; případně Pečující osoba (rodina).</t>
+    <t xml:space="preserve">Aktéři (min. 2, každý min. 4 use casy): Pacient, Tlakoměr.</t>
   </si>
   <si>
     <t xml:space="preserve">7.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Pacient: přihlásit se; spárovat tlakoměr; provést měření podle průvodce; prohlížet historii tlaku a graf; ručně zadat hodnotu; nastavit připomínky měření (ráno/večer); zobrazit doporučení lékaře.</t>
+    <t xml:space="preserve">Pacient: přihlásit se; spárovat tlakoměr; provést měření podle průvodce; prohlížet historii tlaku a graf; rychle zaznamenat energetický nápoj; rychle zaznamenat slané jídlo; nastavit připomínky; zobrazit doporučení lékaře.</t>
   </si>
   <si>
     <t xml:space="preserve">7.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Tlakoměr: odeslat naměřené hodnoty (SYS, DIA, puls, čas); oznámit nepravidelný srdeční rytmus; oznámit chybu měření (špatně nasazená manžeta); oznámit stav baterie.</t>
+    <t xml:space="preserve">Tlakoměr: odeslat naměřené hodnoty (SYS, DIA, puls, čas); oznámit nepravidelný srdeční rytmus; oznámit chybu měření; oznámit stav baterie.</t>
   </si>
   <si>
     <t xml:space="preserve">7.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Doplnit vztahy include/extend (např. „Provést měření“ include „Odeslat data na server“).</t>
+    <t xml:space="preserve">Doplnit vztahy include/extend (např. „Provést měření“ include „Odeslat data na server“; „Zobrazit graf“ extend „Zobrazit záznamy životosprávy“).</t>
   </si>
   <si>
     <t xml:space="preserve">7.5</t>
@@ -724,7 +745,7 @@
     <t xml:space="preserve">7.6</t>
   </si>
   <si>
-    <t xml:space="preserve">Ke 2–3 klíčovým use casům napsat krátký scénář (aktér, předpoklady, hlavní tok, alternativní tok).</t>
+    <t xml:space="preserve">Ke 2–3 klíčovým use casům napsat krátký scénář (měření, rychlý záznam energetického nápoje).</t>
   </si>
   <si>
     <t xml:space="preserve">7.7</t>
@@ -793,43 +814,49 @@
     <t xml:space="preserve">10.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Moduly aplikace: komunikace s tlakoměrem, průvodce měřením, lokální úložiště, synchronizace, sledování aktivity, připomínky.</t>
+    <t xml:space="preserve">Moduly aplikace: komunikace s tlakoměrem, průvodce měřením, rychlý záznam životosprávy, lokální úložiště, synchronizace, sledování aktivity, připomínky, motivační prvky.</t>
   </si>
   <si>
     <t xml:space="preserve">10.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Fyzická aktivita: výchozí volba = senzory telefonu (kroky, aktivní minuty), volitelně náramek/hodinky. Ověřit s vyučujícím (viz list Rozhodnutí).</t>
+    <t xml:space="preserve">Rychlý záznam: energetický nápoj (+1 plechovka, volitelně káva), slané jídlo (málo / středně / hodně). Žádné vážení jídla ani databáze potravin. Data zadává pacient ručně – uvést jako omezení.</t>
   </si>
   <si>
     <t xml:space="preserve">10.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Uvést požadavky na zařízení (mobil vs. PC – volba je na nás; OS, Bluetooth, oprávnění).</t>
+    <t xml:space="preserve">Fyzická aktivita: výchozí volba = senzory telefonu (kroky, aktivní minuty), volitelně náramek/hodinky. Ověřit s vyučujícími (list Rozhodnutí).</t>
   </si>
   <si>
     <t xml:space="preserve">10.5</t>
   </si>
   <si>
+    <t xml:space="preserve">Uvést požadavky na zařízení (mobilní aplikace; OS, Bluetooth, oprávnění).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Napsat text (cca 1 strana) a zkontrolovat soulad s component diagramem.</t>
   </si>
   <si>
     <t xml:space="preserve">11.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Obrazovky: přihlášení, dashboard (poslední tlak + barevný semafor podle limitů), průvodce měřením, historie s grafem tlak + kroky, připomínky, spárování tlakoměru.</t>
+    <t xml:space="preserve">Obrazovky: přihlášení, dashboard (poslední tlak + semafor, dnešní nápoje a sůl, kroky), průvodce měřením, rychlý záznam (velká tlačítka, max. 3 klepnutí), historie s grafem tlaku a vyznačenými záznamy, připomínky, spárování tlakoměru.</t>
   </si>
   <si>
     <t xml:space="preserve">11.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Nakreslit wireframy (draw.io nebo Figma).</t>
+    <t xml:space="preserve">Motivační prvky: série dnů bez energetického nápoje, týdenní souhrn („tlak vs. energetické nápoje“).</t>
   </si>
   <si>
     <t xml:space="preserve">11.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Přizpůsobit seniorům: velké písmo, vysoký kontrast, málo kroků, automatické odeslání.</t>
+    <t xml:space="preserve">Nakreslit wireframy (draw.io nebo Figma); moderní vzhled pro mladé uživatele, tmavý režim.</t>
   </si>
   <si>
     <t xml:space="preserve">11.4</t>
@@ -883,25 +910,25 @@
     <t xml:space="preserve">13.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Aktéři (min. 2, každý min. 4 use casy): Pacient, Lékař; případně Pečující osoba (jen čtení) a Administrátor.</t>
+    <t xml:space="preserve">Aktéři (min. 2, každý min. 4 use casy): Pacient, Lékař; případně Administrátor.</t>
   </si>
   <si>
     <t xml:space="preserve">13.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Pacient: přihlásit se; prohlížet měření a grafy; zobrazit týdenní průměry; exportovat data; číst doporučení lékaře.</t>
+    <t xml:space="preserve">Pacient: přihlásit se; prohlížet měření a grafy; zobrazit týdenní souhrn tlaku a životosprávy; exportovat data; číst doporučení lékaře.</t>
   </si>
   <si>
     <t xml:space="preserve">13.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Lékař: seznam pacientů seřazený podle rizika; detail pacienta (tlak + aktivita); nastavit individuální cílový tlak a limity alertů; potvrdit/vyřešit alert; editovat záznam; zapsat doporučení / změnu medikace.</t>
+    <t xml:space="preserve">Lékař: seznam pacientů seřazený podle rizika; detail pacienta (tlak + aktivita + sůl a nápoje v jednom grafu); nastavit individuální cílový tlak a limity alertů; nastavit doporučený limit energetických nápojů; potvrdit/vyřešit alert; zapsat doporučení.</t>
   </si>
   <si>
     <t xml:space="preserve">13.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Administrátor: správa uživatelů, přiřazení pacienta lékaři, správa rolí, udělení přístupu pečující osobě.</t>
+    <t xml:space="preserve">Administrátor: správa uživatelů, přiřazení pacienta lékaři, správa rolí.</t>
   </si>
   <si>
     <t xml:space="preserve">13.5</t>
@@ -946,13 +973,13 @@
     <t xml:space="preserve">15.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Sestavit matici oprávnění: role × akce (prohlížet / editovat / mazat / exportovat) – pacient jen prohlíží, lékař prohlíží a edituje, admin spravuje.</t>
+    <t xml:space="preserve">Matice oprávnění: role × akce (prohlížet / editovat / mazat / exportovat) – pacient prohlíží a zadává životosprávu, lékař prohlíží, edituje a nastavuje limity, admin spravuje.</t>
   </si>
   <si>
     <t xml:space="preserve">15.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Popsat hlavní moduly portálu: přehled pacientů, detail a grafy, alerty, správa uživatelů.</t>
+    <t xml:space="preserve">Popsat hlavní moduly: přehled pacientů, detail s kombinovaným grafem (tlak, aktivita, sůl, energetické nápoje), alerty, doporučení, správa uživatelů.</t>
   </si>
   <si>
     <t xml:space="preserve">15.4</t>
@@ -964,7 +991,7 @@
     <t xml:space="preserve">16.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Sepsat seznam obrazovek: přihlášení, dashboard lékaře (pacienti + alerty), detail pacienta s grafy, editace záznamu, pohled pacienta, administrace.</t>
+    <t xml:space="preserve">Obrazovky: přihlášení, dashboard lékaře (pacienti + alerty), detail pacienta s kombinovaným grafem tlak × životospráva, nastavení limitů, pohled pacienta, administrace.</t>
   </si>
   <si>
     <t xml:space="preserve">16.2</t>
@@ -1069,25 +1096,25 @@
     <t xml:space="preserve">20.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Navrhnout tabulky (min. 6): Uzivatel, Role, Pacient, Lekar, Zarizeni (tlakoměr), MereniTlaku, Aktivita, LimitAlertu, Alert, Doporuceni, SynchronizaceNIS.</t>
+    <t xml:space="preserve">Navrhnout tabulky (min. 6): Uzivatel, Role, Pacient, Lekar, Zarizeni (tlakoměr), MereniTlaku, Aktivita, ZaznamZivotospravy, LimitAlertu, Alert, Doporuceni, SynchronizaceNIS.</t>
   </si>
   <si>
     <t xml:space="preserve">20.3</t>
   </si>
   <si>
-    <t xml:space="preserve">MereniTlaku min.: id, pacient_id, zarizeni_id, systolicky, diastolicky, puls, nepravidelny_rytmus, cas_mereni, zdroj (BLE/ručně), synchronizovano_nis.</t>
+    <t xml:space="preserve">MereniTlaku: id, pacient_id, zarizeni_id, systolicky, diastolicky, puls, nepravidelny_rytmus, cas_mereni, zdroj (BLE/ručně), synchronizovano_nis.</t>
   </si>
   <si>
     <t xml:space="preserve">20.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Každé tabulce dát min. 4 sloupce s datovými typy, primární a cizí klíče.</t>
+    <t xml:space="preserve">ZaznamZivotospravy: id, pacient_id, typ (energeticky_napoj / kava / slane_jidlo), mnozstvi (kusy nebo málo/středně/hodně), cas_zaznamu, poznamka.</t>
   </si>
   <si>
     <t xml:space="preserve">20.5</t>
   </si>
   <si>
-    <t xml:space="preserve">Určit vztahy a kardinality (1:N, M:N přes spojovací tabulku – např. lékař × pacient).</t>
+    <t xml:space="preserve">Každé tabulce dát min. 4 sloupce s datovými typy, primární a cizí klíče; určit vztahy a kardinality.</t>
   </si>
   <si>
     <t xml:space="preserve">20.6</t>
@@ -1210,7 +1237,7 @@
     <t xml:space="preserve">25.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Nastudovat základy HL7 FHIR (resources, REST API, bundles). Výchozí verze R4 – ověřit s vyučujícím.</t>
+    <t xml:space="preserve">Nastudovat základy HL7 FHIR (resources, REST API, bundles). Výchozí verze R4 – ověřit s vyučujícími.</t>
   </si>
   <si>
     <t xml:space="preserve">25.2</t>
@@ -1222,49 +1249,49 @@
     <t xml:space="preserve">25.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Směr komunikace: výchozí = odesílání měření do NIS; volitelně načítání základních údajů pacienta z NIS. Ověřit s vyučujícím (viz list Rozhodnutí).</t>
+    <t xml:space="preserve">Životospráva: rozhodnout, zda posílat do NIS – výchozí návrh = týdenní souhrn jako Observation s kategorií social-history (počet energetických nápojů, dny se slaným jídlem). Ověřit s vyučujícími.</t>
   </si>
   <si>
     <t xml:space="preserve">25.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Popsat průběh synchronizace: nesynchronizovaná data z DB → převod na FHIR → odeslání → potvrzení → označení v DB.</t>
+    <t xml:space="preserve">Směr komunikace: výchozí = odesílání do NIS; volitelně načítání základních údajů pacienta z NIS.</t>
   </si>
   <si>
     <t xml:space="preserve">25.5</t>
   </si>
   <si>
-    <t xml:space="preserve">Popsat nastavení periody a mailových notifikací při ztrátě spojení / dlouhodobé nedostupnosti NIS.</t>
+    <t xml:space="preserve">Popsat průběh synchronizace a nastavení periody a mailových notifikací při výpadku NIS.</t>
   </si>
   <si>
     <t xml:space="preserve">25.6</t>
   </si>
   <si>
-    <t xml:space="preserve">Napsat text (cca 1,5 strany) včetně mapovací tabulky; případně přidat ukázku FHIR zprávy (JSON).</t>
+    <t xml:space="preserve">Napsat text (cca 1,5 strany) včetně mapovací tabulky; případně ukázka FHIR zprávy (JSON).</t>
   </si>
   <si>
     <t xml:space="preserve">26.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Řešený problém: hypertenze – výskyt v ČR, rizika (mrtvice, infarkt, selhání ledvin), špatná kontrola tlaku u léčených pacientů. Čísla dohledat a ocitovat.</t>
+    <t xml:space="preserve">Řešený problém: hypertenze u mladých dospělých – často nediagnostikovaná nebo podceňovaná, souvisí se životním stylem. Čísla dohledat a ocitovat.</t>
   </si>
   <si>
     <t xml:space="preserve">26.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Úvod do problematiky: telemedicína, domácí měření tlaku podle ESH 2023, vliv fyzické aktivity na tlak.</t>
+    <t xml:space="preserve">Vliv soli na tlak a krátkodobý vliv energetických nápojů (kofein) – dohledat studie a doporučení (ESH 2023, WHO doporučení pro příjem soli).</t>
   </si>
   <si>
     <t xml:space="preserve">26.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Cílová skupina: dospělí s léčenou hypertenzí (úprava léků, nekontrolovaný tlak, vysoké KV riziko, senioři); vyloučit děti a těhotné.</t>
+    <t xml:space="preserve">Cílová skupina: dospělí 18–40 let s léčenou hypertenzí; vyloučit děti/dospívající (jiné normy, souhlas rodičů) a těhotné. Systém neslouží k diagnostice – sekundární hypertenzi musí vyloučit lékař.</t>
   </si>
   <si>
     <t xml:space="preserve">26.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Přehled současných řešení – ta důležitá: aplikace výrobců tlakoměrů (např. Omron, Withings), zdravotní platformy telefonů, telemedicínské programy nemocnic; srovnat v tabulce.</t>
+    <t xml:space="preserve">Přehled současných řešení – ta důležitá (aplikace výrobců tlakoměrů např. Omron, Withings; zdravotní platformy telefonů; nemocniční programy). Srovnat v tabulce a ukázat, že nepropojují tlak s životosprávou.</t>
   </si>
   <si>
     <t xml:space="preserve">26.5</t>
@@ -1315,13 +1342,13 @@
     <t xml:space="preserve">28.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Porovnat se současnými řešeními z Úvodu (tabulka výhod/nevýhod).</t>
+    <t xml:space="preserve">Hlavní výhoda: propojení tlaku, aktivity a životosprávy (sůl, energetické nápoje) pro mladé pacienty – porovnat se současnými řešeními (tabulka).</t>
   </si>
   <si>
     <t xml:space="preserve">28.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Uvést omezení návrhu a možná rozšíření.</t>
+    <t xml:space="preserve">Omezení: ruční zadávání životosprávy, závislost na ochotě pacienta; možná rozšíření (napojení na nákupní/jídelní aplikace).</t>
   </si>
   <si>
     <t xml:space="preserve">28.4</t>
@@ -2334,7 +2361,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -2486,7 +2513,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2574,7 +2601,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
@@ -2588,89 +2615,89 @@
         <v>58</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>49</v>
@@ -2681,13 +2708,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>49</v>
@@ -2698,13 +2725,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>78</v>
+        <v>27</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>49</v>
@@ -2715,13 +2742,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>49</v>
@@ -2732,13 +2759,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>49</v>
@@ -2751,17 +2778,17 @@
       <c r="B18" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>81</v>
+      <c r="C18" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" s="11" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E18" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
@@ -2769,13 +2796,13 @@
         <v>88</v>
       </c>
       <c r="C19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="E19" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2786,13 +2813,13 @@
         <v>91</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2800,16 +2827,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2817,16 +2844,67 @@
         <v>18</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>87</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2860,12 +2938,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2873,25 +2951,25 @@
         <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2899,23 +2977,23 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>46303</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G5" s="10"/>
       <c r="H5" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A5,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A5)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A5,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A5)</f>
         <v>4 / 4</v>
       </c>
     </row>
@@ -2924,23 +3002,23 @@
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>46316</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G6" s="10"/>
       <c r="H6" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A6,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A6)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A6,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A6)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -2949,23 +3027,23 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>46309</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A7,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A7)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A7,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A7)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -2974,23 +3052,23 @@
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>46337</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A8,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A8)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A8,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A8)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -2999,23 +3077,23 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>46330</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A9,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A9)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A9,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A9)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -3024,23 +3102,23 @@
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>46323</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A10,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A10)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A10,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A10)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -3049,10 +3127,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>3</v>
@@ -3061,11 +3139,11 @@
         <v>46323</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A11,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A11)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A11,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A11)</f>
         <v>0 / 7</v>
       </c>
     </row>
@@ -3074,10 +3152,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>3</v>
@@ -3086,11 +3164,11 @@
         <v>46330</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A12,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A12)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A12,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A12)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3099,10 +3177,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>3</v>
@@ -3111,11 +3189,11 @@
         <v>46330</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A13,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A13)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A13,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A13)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -3124,10 +3202,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>3</v>
@@ -3136,12 +3214,12 @@
         <v>46337</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A14,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A14)</f>
-        <v>0 / 5</v>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A14,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A14)</f>
+        <v>0 / 6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3149,10 +3227,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>3</v>
@@ -3161,11 +3239,11 @@
         <v>46351</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A15,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A15)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A15,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A15)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -3174,10 +3252,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>3</v>
@@ -3186,11 +3264,11 @@
         <v>46358</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G16" s="10"/>
       <c r="H16" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A16,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A16)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A16,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A16)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3199,10 +3277,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>4</v>
@@ -3211,11 +3289,11 @@
         <v>46323</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A17,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A17)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A17,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A17)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3224,10 +3302,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>4</v>
@@ -3236,11 +3314,11 @@
         <v>46330</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A18,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A18)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A18,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A18)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3249,10 +3327,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>4</v>
@@ -3261,11 +3339,11 @@
         <v>46337</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A19,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A19)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A19,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A19)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3274,10 +3352,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>4</v>
@@ -3286,11 +3364,11 @@
         <v>46351</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A20,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A20)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A20,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A20)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3299,10 +3377,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>4</v>
@@ -3311,11 +3389,11 @@
         <v>46358</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A21,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A21)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A21,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A21)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3324,10 +3402,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>5</v>
@@ -3336,11 +3414,11 @@
         <v>46323</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A22,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A22)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A22,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A22)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3349,10 +3427,10 @@
         <v>19</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>5</v>
@@ -3361,11 +3439,11 @@
         <v>46330</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A23,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A23)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A23,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A23)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3374,10 +3452,10 @@
         <v>20</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>5</v>
@@ -3386,11 +3464,11 @@
         <v>46330</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A24,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A24)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A24,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A24)</f>
         <v>0 / 8</v>
       </c>
     </row>
@@ -3399,10 +3477,10 @@
         <v>21</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>5</v>
@@ -3411,11 +3489,11 @@
         <v>46337</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A25,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A25)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A25,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A25)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -3424,10 +3502,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>5</v>
@@ -3436,11 +3514,11 @@
         <v>46358</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G26" s="10"/>
       <c r="H26" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A26,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A26)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A26,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A26)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3449,10 +3527,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>6</v>
@@ -3461,11 +3539,11 @@
         <v>46323</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G27" s="10"/>
       <c r="H27" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A27,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A27)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A27,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A27)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3474,10 +3552,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>6</v>
@@ -3486,11 +3564,11 @@
         <v>46330</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G28" s="10"/>
       <c r="H28" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A28,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A28)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A28,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A28)</f>
         <v>0 / 3</v>
       </c>
     </row>
@@ -3499,10 +3577,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>6</v>
@@ -3511,11 +3589,11 @@
         <v>46337</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G29" s="10"/>
       <c r="H29" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A29,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A29)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A29,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A29)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3524,10 +3602,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>6</v>
@@ -3536,11 +3614,11 @@
         <v>46344</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G30" s="10"/>
       <c r="H30" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A30,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A30)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A30,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A30)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3549,10 +3627,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>6</v>
@@ -3561,11 +3639,11 @@
         <v>46358</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G31" s="10"/>
       <c r="H31" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A31,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A31)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A31,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A31)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -3574,23 +3652,23 @@
         <v>28</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>46358</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G32" s="10"/>
       <c r="H32" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A32,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A32)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A32,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A32)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3599,23 +3677,23 @@
         <v>29</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>46365</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G33" s="10"/>
       <c r="H33" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A33,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A33)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A33,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A33)</f>
         <v>0 / 3</v>
       </c>
     </row>
@@ -3624,23 +3702,23 @@
         <v>30</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>46365</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G34" s="10"/>
       <c r="H34" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A34,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A34)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A34,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A34)</f>
         <v>0 / 5</v>
       </c>
     </row>
@@ -3649,23 +3727,23 @@
         <v>31</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>46365</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A35,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A35)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A35,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A35)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3674,23 +3752,23 @@
         <v>32</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>46372</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A36,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A36)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A36,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A36)</f>
         <v>0 / 6</v>
       </c>
     </row>
@@ -3699,23 +3777,23 @@
         <v>33</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>46365</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G37" s="10"/>
       <c r="H37" s="13" t="str">
-        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$170,A37,'Osnova kroků'!$F$5:$F$170,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$170,A37)</f>
+        <f aca="false">COUNTIFS('Osnova kroků'!$A$5:$A$171,A37,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A37)</f>
         <v>0 / 4</v>
       </c>
     </row>
@@ -3751,7 +3829,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G171"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -3765,35 +3843,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3801,20 +3879,20 @@
         <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E5" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A5,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G5" s="10"/>
     </row>
@@ -3824,17 +3902,17 @@
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E6" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A6,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G6" s="10"/>
     </row>
@@ -3844,17 +3922,17 @@
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E7" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A7,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G7" s="10"/>
     </row>
@@ -3864,17 +3942,17 @@
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E8" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A8,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G8" s="10"/>
     </row>
@@ -3883,20 +3961,20 @@
         <v>2</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E9" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A9,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G9" s="10"/>
     </row>
@@ -3906,17 +3984,17 @@
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="15" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E10" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A10,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G10" s="10"/>
     </row>
@@ -3926,17 +4004,17 @@
       </c>
       <c r="B11" s="16"/>
       <c r="C11" s="15" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E11" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A11,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G11" s="10"/>
     </row>
@@ -3946,37 +4024,37 @@
       </c>
       <c r="B12" s="16"/>
       <c r="C12" s="15" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E12" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A12,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G12" s="10"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="n">
         <v>2</v>
       </c>
       <c r="B13" s="16"/>
       <c r="C13" s="15" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E13" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A13,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G13" s="10"/>
     </row>
@@ -3986,17 +4064,17 @@
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="15" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E14" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A14,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G14" s="10"/>
     </row>
@@ -4005,20 +4083,20 @@
         <v>3</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="E15" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A15,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G15" s="10"/>
     </row>
@@ -4028,17 +4106,17 @@
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="6" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E16" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A16,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G16" s="10"/>
     </row>
@@ -4048,17 +4126,17 @@
       </c>
       <c r="B17" s="14"/>
       <c r="C17" s="6" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E17" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A17,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G17" s="10"/>
     </row>
@@ -4068,17 +4146,17 @@
       </c>
       <c r="B18" s="14"/>
       <c r="C18" s="6" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="E18" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A18,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G18" s="10"/>
     </row>
@@ -4088,17 +4166,17 @@
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="6" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E19" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A19,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G19" s="10"/>
     </row>
@@ -4107,20 +4185,20 @@
         <v>4</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E20" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A20,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G20" s="10"/>
     </row>
@@ -4130,17 +4208,17 @@
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="15" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E21" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A21,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G21" s="10"/>
     </row>
@@ -4150,17 +4228,17 @@
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="15" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E22" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A22,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G22" s="10"/>
     </row>
@@ -4170,17 +4248,17 @@
       </c>
       <c r="B23" s="16"/>
       <c r="C23" s="15" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E23" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A23,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G23" s="10"/>
     </row>
@@ -4190,17 +4268,17 @@
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="15" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E24" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A24,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G24" s="10"/>
     </row>
@@ -4210,17 +4288,17 @@
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="15" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E25" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A25,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G25" s="10"/>
     </row>
@@ -4229,20 +4307,20 @@
         <v>5</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E26" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A26,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G26" s="10"/>
     </row>
@@ -4252,17 +4330,17 @@
       </c>
       <c r="B27" s="14"/>
       <c r="C27" s="6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="E27" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A27,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G27" s="10"/>
     </row>
@@ -4272,17 +4350,17 @@
       </c>
       <c r="B28" s="14"/>
       <c r="C28" s="6" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E28" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A28,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G28" s="10"/>
     </row>
@@ -4292,17 +4370,17 @@
       </c>
       <c r="B29" s="14"/>
       <c r="C29" s="6" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E29" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A29,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G29" s="10"/>
     </row>
@@ -4312,17 +4390,17 @@
       </c>
       <c r="B30" s="14"/>
       <c r="C30" s="6" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="E30" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A30,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G30" s="10"/>
     </row>
@@ -4331,20 +4409,20 @@
         <v>6</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E31" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A31,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G31" s="10"/>
     </row>
@@ -4354,17 +4432,17 @@
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="15" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E32" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A32,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F32" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G32" s="10"/>
     </row>
@@ -4374,17 +4452,17 @@
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="15" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E33" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A33,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G33" s="10"/>
     </row>
@@ -4394,17 +4472,17 @@
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="15" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E34" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A34,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G34" s="10"/>
     </row>
@@ -4414,17 +4492,17 @@
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="15" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E35" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A35,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G35" s="10"/>
     </row>
@@ -4433,20 +4511,20 @@
         <v>7</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E36" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A36,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G36" s="10"/>
     </row>
@@ -4456,37 +4534,37 @@
       </c>
       <c r="B37" s="14"/>
       <c r="C37" s="6" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E37" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A37,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G37" s="10"/>
     </row>
-    <row r="38" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E38" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A38,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G38" s="10"/>
     </row>
@@ -4496,17 +4574,17 @@
       </c>
       <c r="B39" s="14"/>
       <c r="C39" s="6" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E39" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A39,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G39" s="10"/>
     </row>
@@ -4516,17 +4594,17 @@
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="6" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E40" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A40,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G40" s="10"/>
     </row>
@@ -4536,17 +4614,17 @@
       </c>
       <c r="B41" s="14"/>
       <c r="C41" s="6" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E41" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A41,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G41" s="10"/>
     </row>
@@ -4556,17 +4634,17 @@
       </c>
       <c r="B42" s="14"/>
       <c r="C42" s="6" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E42" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A42,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G42" s="10"/>
     </row>
@@ -4575,20 +4653,20 @@
         <v>8</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E43" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A43,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G43" s="10"/>
     </row>
@@ -4598,17 +4676,17 @@
       </c>
       <c r="B44" s="16"/>
       <c r="C44" s="15" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E44" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A44,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G44" s="10"/>
     </row>
@@ -4618,17 +4696,17 @@
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="15" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E45" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A45,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G45" s="10"/>
     </row>
@@ -4638,17 +4716,17 @@
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="15" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E46" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A46,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G46" s="10"/>
     </row>
@@ -4657,20 +4735,20 @@
         <v>9</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E47" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A47,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G47" s="10"/>
     </row>
@@ -4680,17 +4758,17 @@
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="6" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="E48" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A48,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G48" s="10"/>
     </row>
@@ -4700,17 +4778,17 @@
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="6" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E49" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A49,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G49" s="10"/>
     </row>
@@ -4720,17 +4798,17 @@
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="6" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="E50" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A50,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G50" s="10"/>
     </row>
@@ -4740,17 +4818,17 @@
       </c>
       <c r="B51" s="14"/>
       <c r="C51" s="6" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="E51" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A51,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G51" s="10"/>
     </row>
@@ -4759,60 +4837,60 @@
         <v>10</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="E52" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A52,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G52" s="10"/>
     </row>
-    <row r="53" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="n">
         <v>10</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="15" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E53" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A53,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G53" s="10"/>
     </row>
-    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="n">
         <v>10</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="15" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E54" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A54,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F54" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G54" s="10"/>
     </row>
@@ -4822,17 +4900,17 @@
       </c>
       <c r="B55" s="16"/>
       <c r="C55" s="15" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="E55" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A55,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F55" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G55" s="10"/>
     </row>
@@ -4842,59 +4920,59 @@
       </c>
       <c r="B56" s="16"/>
       <c r="C56" s="15" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E56" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A56,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F56" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G56" s="10"/>
     </row>
-    <row r="57" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E57" s="6" t="str">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B57" s="16"/>
+      <c r="C57" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="E57" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A57,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G57" s="10"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B58" s="14"/>
+      <c r="B58" s="14" t="s">
+        <v>127</v>
+      </c>
       <c r="C58" s="6" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="E58" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A58,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G58" s="10"/>
     </row>
@@ -4904,37 +4982,37 @@
       </c>
       <c r="B59" s="14"/>
       <c r="C59" s="6" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E59" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A59,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G59" s="10"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B60" s="14"/>
       <c r="C60" s="6" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="E60" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A60,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F60" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G60" s="10"/>
     </row>
@@ -4944,79 +5022,79 @@
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="6" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E61" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A61,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F61" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G61" s="10"/>
     </row>
-    <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>271</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>272</v>
-      </c>
-      <c r="E62" s="15" t="str">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B62" s="14"/>
+      <c r="C62" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E62" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A62,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F62" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G62" s="10"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B63" s="16"/>
+      <c r="B63" s="16" t="s">
+        <v>128</v>
+      </c>
       <c r="C63" s="15" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E63" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A63,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F63" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G63" s="10"/>
     </row>
-    <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="15" t="n">
         <v>12</v>
       </c>
       <c r="B64" s="16"/>
       <c r="C64" s="15" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E64" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A64,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F64" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G64" s="10"/>
     </row>
@@ -5026,37 +5104,37 @@
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E65" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A65,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F65" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G65" s="10"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="15" t="n">
         <v>12</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="15" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="E66" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A66,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G66" s="10"/>
     </row>
@@ -5066,39 +5144,37 @@
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="15" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E67" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A67,Úkoly!$A$5:$A$37,0))</f>
         <v>1 – Pacientská část</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G67" s="10"/>
     </row>
-    <row r="68" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="E68" s="6" t="str">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B68" s="16"/>
+      <c r="C68" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E68" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A68,Úkoly!$A$5:$A$37,0))</f>
-        <v>2 – Webový portál</v>
+        <v>1 – Pacientská část</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G68" s="10"/>
     </row>
@@ -5106,59 +5182,61 @@
       <c r="A69" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B69" s="14"/>
+      <c r="B69" s="14" t="s">
+        <v>130</v>
+      </c>
       <c r="C69" s="6" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E69" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A69,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G69" s="10"/>
     </row>
-    <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B70" s="14"/>
       <c r="C70" s="6" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E70" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A70,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G70" s="10"/>
     </row>
-    <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B71" s="14"/>
       <c r="C71" s="6" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E71" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A71,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G71" s="10"/>
     </row>
@@ -5168,17 +5246,17 @@
       </c>
       <c r="B72" s="14"/>
       <c r="C72" s="6" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="E72" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A72,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G72" s="10"/>
     </row>
@@ -5188,79 +5266,79 @@
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="6" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>233</v>
+        <v>301</v>
       </c>
       <c r="E73" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A73,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G73" s="10"/>
     </row>
-    <row r="74" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B74" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="E74" s="15" t="str">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" s="14"/>
+      <c r="C74" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E74" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A74,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G74" s="10"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B75" s="16"/>
+      <c r="B75" s="16" t="s">
+        <v>131</v>
+      </c>
       <c r="C75" s="15" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="E75" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A75,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G75" s="10"/>
     </row>
-    <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="15" t="n">
         <v>14</v>
       </c>
       <c r="B76" s="16"/>
       <c r="C76" s="15" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E76" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A76,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G76" s="10"/>
     </row>
@@ -5270,39 +5348,37 @@
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="15" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="E77" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A77,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E78" s="6" t="str">
+      <c r="A78" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B78" s="16"/>
+      <c r="C78" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D78" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="E78" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A78,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G78" s="10"/>
     </row>
@@ -5310,101 +5386,103 @@
       <c r="A79" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B79" s="14"/>
+      <c r="B79" s="14" t="s">
+        <v>132</v>
+      </c>
       <c r="C79" s="6" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="E79" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A79,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G79" s="10"/>
     </row>
-    <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B80" s="14"/>
       <c r="C80" s="6" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E80" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A80,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G80" s="10"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B81" s="14"/>
       <c r="C81" s="6" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="E81" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A81,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G81" s="10"/>
     </row>
-    <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C82" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="E82" s="15" t="str">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B82" s="14"/>
+      <c r="C82" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="E82" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A82,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G82" s="10"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B83" s="16"/>
+      <c r="B83" s="16" t="s">
+        <v>133</v>
+      </c>
       <c r="C83" s="15" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="E83" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A83,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G83" s="10"/>
     </row>
@@ -5414,17 +5492,17 @@
       </c>
       <c r="B84" s="16"/>
       <c r="C84" s="15" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>268</v>
+        <v>322</v>
       </c>
       <c r="E84" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A84,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G84" s="10"/>
     </row>
@@ -5434,39 +5512,37 @@
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="15" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E85" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A85,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G85" s="10"/>
     </row>
-    <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E86" s="6" t="str">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="B86" s="16"/>
+      <c r="C86" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D86" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E86" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A86,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G86" s="10"/>
     </row>
@@ -5474,19 +5550,21 @@
       <c r="A87" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B87" s="14"/>
+      <c r="B87" s="14" t="s">
+        <v>134</v>
+      </c>
       <c r="C87" s="6" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="E87" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A87,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F87" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G87" s="10"/>
     </row>
@@ -5496,37 +5574,37 @@
       </c>
       <c r="B88" s="14"/>
       <c r="C88" s="6" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E88" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A88,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G88" s="10"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="n">
         <v>17</v>
       </c>
       <c r="B89" s="14"/>
       <c r="C89" s="6" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E89" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A89,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F89" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G89" s="10"/>
     </row>
@@ -5536,17 +5614,17 @@
       </c>
       <c r="B90" s="14"/>
       <c r="C90" s="6" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E90" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A90,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G90" s="10"/>
     </row>
@@ -5556,39 +5634,37 @@
       </c>
       <c r="B91" s="14"/>
       <c r="C91" s="6" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E91" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A91,Úkoly!$A$5:$A$37,0))</f>
         <v>2 – Webový portál</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G91" s="10"/>
     </row>
-    <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="B92" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>328</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>329</v>
-      </c>
-      <c r="E92" s="15" t="str">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B92" s="14"/>
+      <c r="C92" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E92" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A92,Úkoly!$A$5:$A$37,0))</f>
-        <v>3 – WEB API + databáze</v>
+        <v>2 – Webový portál</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G92" s="10"/>
     </row>
@@ -5596,39 +5672,41 @@
       <c r="A93" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B93" s="16"/>
+      <c r="B93" s="16" t="s">
+        <v>136</v>
+      </c>
       <c r="C93" s="15" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E93" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A93,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G93" s="10"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="15" t="n">
         <v>18</v>
       </c>
       <c r="B94" s="16"/>
       <c r="C94" s="15" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E94" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A94,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G94" s="10"/>
     </row>
@@ -5638,39 +5716,37 @@
       </c>
       <c r="B95" s="16"/>
       <c r="C95" s="15" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>233</v>
+        <v>342</v>
       </c>
       <c r="E95" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A95,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G95" s="10"/>
     </row>
-    <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E96" s="6" t="str">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B96" s="16"/>
+      <c r="C96" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="E96" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A96,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G96" s="10"/>
     </row>
@@ -5678,39 +5754,41 @@
       <c r="A97" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B97" s="14"/>
+      <c r="B97" s="14" t="s">
+        <v>137</v>
+      </c>
       <c r="C97" s="6" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E97" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A97,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G97" s="10"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="n">
         <v>19</v>
       </c>
       <c r="B98" s="14"/>
       <c r="C98" s="6" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E98" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A98,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G98" s="10"/>
     </row>
@@ -5720,39 +5798,37 @@
       </c>
       <c r="B99" s="14"/>
       <c r="C99" s="6" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E99" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A99,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G99" s="10"/>
     </row>
-    <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C100" s="15" t="s">
-        <v>343</v>
-      </c>
-      <c r="D100" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="E100" s="15" t="str">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B100" s="14"/>
+      <c r="C100" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="E100" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A100,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G100" s="10"/>
     </row>
@@ -5760,99 +5836,101 @@
       <c r="A101" s="15" t="n">
         <v>20</v>
       </c>
-      <c r="B101" s="16"/>
+      <c r="B101" s="16" t="s">
+        <v>138</v>
+      </c>
       <c r="C101" s="15" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E101" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A101,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G101" s="10"/>
     </row>
-    <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="15" t="n">
         <v>20</v>
       </c>
       <c r="B102" s="16"/>
       <c r="C102" s="15" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E102" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A102,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G102" s="10"/>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="15" t="n">
         <v>20</v>
       </c>
       <c r="B103" s="16"/>
       <c r="C103" s="15" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E103" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A103,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G103" s="10"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="15" t="n">
         <v>20</v>
       </c>
       <c r="B104" s="16"/>
       <c r="C104" s="15" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E104" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A104,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G104" s="10"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="15" t="n">
         <v>20</v>
       </c>
       <c r="B105" s="16"/>
       <c r="C105" s="15" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E105" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A105,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G105" s="10"/>
     </row>
@@ -5862,17 +5940,17 @@
       </c>
       <c r="B106" s="16"/>
       <c r="C106" s="15" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E106" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A106,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F106" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G106" s="10"/>
     </row>
@@ -5882,79 +5960,79 @@
       </c>
       <c r="B107" s="16"/>
       <c r="C107" s="15" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E107" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A107,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F107" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G107" s="10"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="B108" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="E108" s="6" t="str">
+      <c r="A108" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B108" s="16"/>
+      <c r="C108" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="E108" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A108,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G108" s="10"/>
     </row>
-    <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B109" s="14"/>
+      <c r="B109" s="14" t="s">
+        <v>139</v>
+      </c>
       <c r="C109" s="6" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E109" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A109,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F109" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G109" s="10"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="n">
         <v>21</v>
       </c>
       <c r="B110" s="14"/>
       <c r="C110" s="6" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E110" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A110,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F110" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G110" s="10"/>
     </row>
@@ -5964,17 +6042,17 @@
       </c>
       <c r="B111" s="14"/>
       <c r="C111" s="6" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E111" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A111,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G111" s="10"/>
     </row>
@@ -5984,59 +6062,59 @@
       </c>
       <c r="B112" s="14"/>
       <c r="C112" s="6" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E112" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A112,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G112" s="10"/>
     </row>
-    <row r="113" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="B113" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="D113" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="E113" s="15" t="str">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B113" s="14"/>
+      <c r="C113" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="E113" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A113,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G113" s="10"/>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B114" s="16"/>
+      <c r="B114" s="16" t="s">
+        <v>140</v>
+      </c>
       <c r="C114" s="15" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="E114" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A114,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G114" s="10"/>
     </row>
@@ -6046,57 +6124,57 @@
       </c>
       <c r="B115" s="16"/>
       <c r="C115" s="15" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="E115" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A115,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F115" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G115" s="10"/>
     </row>
-    <row r="116" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="15" t="n">
         <v>22</v>
       </c>
       <c r="B116" s="16"/>
       <c r="C116" s="15" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E116" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A116,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F116" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G116" s="10"/>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="15" t="n">
         <v>22</v>
       </c>
       <c r="B117" s="16"/>
       <c r="C117" s="15" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="E117" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A117,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G117" s="10"/>
     </row>
@@ -6106,79 +6184,79 @@
       </c>
       <c r="B118" s="16"/>
       <c r="C118" s="15" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="E118" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A118,Úkoly!$A$5:$A$37,0))</f>
         <v>3 – WEB API + databáze</v>
       </c>
       <c r="F118" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G118" s="10"/>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="B119" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="E119" s="6" t="str">
+      <c r="A119" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="B119" s="16"/>
+      <c r="C119" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="E119" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A119,Úkoly!$A$5:$A$37,0))</f>
-        <v>4 – Integrátor NIS (FHIR)</v>
+        <v>3 – WEB API + databáze</v>
       </c>
       <c r="F119" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G119" s="10"/>
     </row>
-    <row r="120" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B120" s="14"/>
+      <c r="B120" s="14" t="s">
+        <v>142</v>
+      </c>
       <c r="C120" s="6" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="E120" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A120,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G120" s="10"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="n">
         <v>23</v>
       </c>
       <c r="B121" s="14"/>
       <c r="C121" s="6" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="E121" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A121,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G121" s="10"/>
     </row>
@@ -6188,39 +6266,37 @@
       </c>
       <c r="B122" s="14"/>
       <c r="C122" s="6" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>233</v>
+        <v>342</v>
       </c>
       <c r="E122" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A122,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F122" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G122" s="10"/>
     </row>
-    <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="B123" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="C123" s="15" t="s">
-        <v>387</v>
-      </c>
-      <c r="D123" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="E123" s="15" t="str">
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B123" s="14"/>
+      <c r="C123" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E123" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A123,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F123" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G123" s="10"/>
     </row>
@@ -6228,121 +6304,123 @@
       <c r="A124" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="B124" s="16"/>
+      <c r="B124" s="16" t="s">
+        <v>143</v>
+      </c>
       <c r="C124" s="15" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="E124" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A124,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F124" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G124" s="10"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="15" t="n">
         <v>24</v>
       </c>
       <c r="B125" s="16"/>
       <c r="C125" s="15" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="E125" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A125,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G125" s="10"/>
     </row>
-    <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="B126" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="E126" s="6" t="str">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="B126" s="16"/>
+      <c r="C126" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="E126" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A126,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G126" s="10"/>
     </row>
-    <row r="127" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B127" s="14"/>
+      <c r="B127" s="14" t="s">
+        <v>144</v>
+      </c>
       <c r="C127" s="6" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E127" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A127,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G127" s="10"/>
     </row>
-    <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="n">
         <v>25</v>
       </c>
       <c r="B128" s="14"/>
       <c r="C128" s="6" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="E128" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A128,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G128" s="10"/>
     </row>
-    <row r="129" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="n">
         <v>25</v>
       </c>
       <c r="B129" s="14"/>
       <c r="C129" s="6" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="E129" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A129,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G129" s="10"/>
     </row>
@@ -6352,17 +6430,17 @@
       </c>
       <c r="B130" s="14"/>
       <c r="C130" s="6" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="E130" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A130,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G130" s="10"/>
     </row>
@@ -6372,39 +6450,37 @@
       </c>
       <c r="B131" s="14"/>
       <c r="C131" s="6" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="E131" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A131,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F131" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G131" s="10"/>
     </row>
     <row r="132" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="B132" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="C132" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="D132" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="E132" s="15" t="str">
+      <c r="A132" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B132" s="14"/>
+      <c r="C132" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="E132" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A132,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G132" s="10"/>
     </row>
@@ -6412,19 +6488,21 @@
       <c r="A133" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="B133" s="16"/>
+      <c r="B133" s="16" t="s">
+        <v>145</v>
+      </c>
       <c r="C133" s="15" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="E133" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A133,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F133" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G133" s="10"/>
     </row>
@@ -6434,17 +6512,17 @@
       </c>
       <c r="B134" s="16"/>
       <c r="C134" s="15" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="E134" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A134,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F134" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G134" s="10"/>
     </row>
@@ -6454,37 +6532,37 @@
       </c>
       <c r="B135" s="16"/>
       <c r="C135" s="15" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E135" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A135,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F135" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G135" s="10"/>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="15" t="n">
         <v>26</v>
       </c>
       <c r="B136" s="16"/>
       <c r="C136" s="15" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="E136" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A136,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G136" s="10"/>
     </row>
@@ -6494,59 +6572,59 @@
       </c>
       <c r="B137" s="16"/>
       <c r="C137" s="15" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E137" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A137,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G137" s="10"/>
     </row>
-    <row r="138" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="B138" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="E138" s="6" t="str">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="B138" s="16"/>
+      <c r="C138" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="E138" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A138,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G138" s="10"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B139" s="14"/>
+      <c r="B139" s="14" t="s">
+        <v>147</v>
+      </c>
       <c r="C139" s="6" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E139" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A139,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F139" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G139" s="10"/>
     </row>
@@ -6556,161 +6634,159 @@
       </c>
       <c r="B140" s="14"/>
       <c r="C140" s="6" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="E140" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A140,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F140" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G140" s="10"/>
     </row>
-    <row r="141" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="6" t="n">
         <v>27</v>
       </c>
       <c r="B141" s="14"/>
       <c r="C141" s="6" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="E141" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A141,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F141" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G141" s="10"/>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="n">
         <v>27</v>
       </c>
       <c r="B142" s="14"/>
       <c r="C142" s="6" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>282</v>
+        <v>432</v>
       </c>
       <c r="E142" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A142,Úkoly!$A$5:$A$37,0))</f>
         <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F142" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G142" s="10"/>
     </row>
-    <row r="143" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="B143" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="C143" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="D143" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="E143" s="15" t="str">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B143" s="14"/>
+      <c r="C143" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E143" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A143,Úkoly!$A$5:$A$37,0))</f>
-        <v>Společně</v>
+        <v>4 – Integrátor NIS (FHIR)</v>
       </c>
       <c r="F143" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G143" s="10"/>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="B144" s="16"/>
+      <c r="B144" s="16" t="s">
+        <v>149</v>
+      </c>
       <c r="C144" s="15" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="E144" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A144,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F144" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G144" s="10"/>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="15" t="n">
         <v>28</v>
       </c>
       <c r="B145" s="16"/>
       <c r="C145" s="15" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E145" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A145,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F145" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G145" s="10"/>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="15" t="n">
         <v>28</v>
       </c>
       <c r="B146" s="16"/>
       <c r="C146" s="15" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="E146" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A146,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F146" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G146" s="10"/>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="B147" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="C147" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="D147" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="E147" s="6" t="str">
+      <c r="A147" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B147" s="16"/>
+      <c r="C147" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="D147" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E147" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A147,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G147" s="10"/>
     </row>
@@ -6718,19 +6794,21 @@
       <c r="A148" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B148" s="14"/>
+      <c r="B148" s="14" t="s">
+        <v>151</v>
+      </c>
       <c r="C148" s="6" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="E148" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A148,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F148" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G148" s="10"/>
     </row>
@@ -6740,59 +6818,59 @@
       </c>
       <c r="B149" s="14"/>
       <c r="C149" s="6" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E149" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A149,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F149" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G149" s="10"/>
     </row>
-    <row r="150" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="B150" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="C150" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="D150" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="E150" s="15" t="str">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B150" s="14"/>
+      <c r="C150" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="E150" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A150,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F150" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G150" s="10"/>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="B151" s="16"/>
+      <c r="B151" s="16" t="s">
+        <v>153</v>
+      </c>
       <c r="C151" s="15" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E151" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A151,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G151" s="10"/>
     </row>
@@ -6802,17 +6880,17 @@
       </c>
       <c r="B152" s="16"/>
       <c r="C152" s="15" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="E152" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A152,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F152" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G152" s="10"/>
     </row>
@@ -6822,59 +6900,57 @@
       </c>
       <c r="B153" s="16"/>
       <c r="C153" s="15" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="E153" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A153,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F153" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G153" s="10"/>
     </row>
-    <row r="154" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="15" t="n">
         <v>30</v>
       </c>
       <c r="B154" s="16"/>
       <c r="C154" s="15" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E154" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A154,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F154" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G154" s="10"/>
     </row>
     <row r="155" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="B155" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="E155" s="6" t="str">
+      <c r="A155" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="B155" s="16"/>
+      <c r="C155" s="15" t="s">
+        <v>456</v>
+      </c>
+      <c r="D155" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="E155" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A155,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G155" s="10"/>
     </row>
@@ -6882,39 +6958,41 @@
       <c r="A156" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B156" s="14"/>
+      <c r="B156" s="14" t="s">
+        <v>155</v>
+      </c>
       <c r="C156" s="6" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="E156" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A156,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F156" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G156" s="10"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="n">
         <v>31</v>
       </c>
       <c r="B157" s="14"/>
       <c r="C157" s="6" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="E157" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A157,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F157" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G157" s="10"/>
     </row>
@@ -6924,79 +7002,77 @@
       </c>
       <c r="B158" s="14"/>
       <c r="C158" s="6" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="E158" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A158,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F158" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G158" s="10"/>
     </row>
-    <row r="159" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="n">
         <v>31</v>
       </c>
       <c r="B159" s="14"/>
       <c r="C159" s="6" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="E159" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A159,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F159" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G159" s="10"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="n">
         <v>31</v>
       </c>
       <c r="B160" s="14"/>
       <c r="C160" s="6" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="E160" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A160,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F160" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G160" s="10"/>
     </row>
-    <row r="161" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="B161" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="C161" s="15" t="s">
-        <v>461</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="E161" s="15" t="str">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B161" s="14"/>
+      <c r="C161" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="E161" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A161,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F161" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G161" s="10"/>
     </row>
@@ -7004,39 +7080,41 @@
       <c r="A162" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="B162" s="16"/>
+      <c r="B162" s="16" t="s">
+        <v>157</v>
+      </c>
       <c r="C162" s="15" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="E162" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A162,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F162" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G162" s="10"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="15" t="n">
         <v>32</v>
       </c>
       <c r="B163" s="16"/>
       <c r="C163" s="15" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="E163" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A163,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F163" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G163" s="10"/>
     </row>
@@ -7046,17 +7124,17 @@
       </c>
       <c r="B164" s="16"/>
       <c r="C164" s="15" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E164" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A164,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G164" s="10"/>
     </row>
@@ -7066,17 +7144,17 @@
       </c>
       <c r="B165" s="16"/>
       <c r="C165" s="15" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="E165" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A165,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G165" s="10"/>
     </row>
@@ -7086,59 +7164,59 @@
       </c>
       <c r="B166" s="16"/>
       <c r="C166" s="15" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="E166" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A166,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F166" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G166" s="10"/>
     </row>
-    <row r="167" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="6" t="n">
-        <v>33</v>
-      </c>
-      <c r="B167" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>474</v>
-      </c>
-      <c r="E167" s="6" t="str">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="B167" s="16"/>
+      <c r="C167" s="15" t="s">
+        <v>480</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="E167" s="15" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A167,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F167" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G167" s="10"/>
     </row>
-    <row r="168" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B168" s="14"/>
+      <c r="B168" s="14" t="s">
+        <v>158</v>
+      </c>
       <c r="C168" s="6" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="E168" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A168,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F168" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G168" s="10"/>
     </row>
@@ -7148,43 +7226,63 @@
       </c>
       <c r="B169" s="14"/>
       <c r="C169" s="6" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="E169" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A169,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G169" s="10"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="n">
         <v>33</v>
       </c>
       <c r="B170" s="14"/>
       <c r="C170" s="6" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E170" s="6" t="str">
         <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A170,Úkoly!$A$5:$A$37,0))</f>
         <v>Společně</v>
       </c>
       <c r="F170" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G170" s="10"/>
     </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B171" s="14"/>
+      <c r="C171" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="E171" s="6" t="str">
+        <f aca="false">INDEX(Úkoly!$D$5:$D$37,MATCH(A171,Úkoly!$A$5:$A$37,0))</f>
+        <v>Společně</v>
+      </c>
+      <c r="F171" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G171" s="10"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G170"/>
-  <conditionalFormatting sqref="F5:F170">
+  <autoFilter ref="A4:G171"/>
+  <conditionalFormatting sqref="F5:F171">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Hotovo"</formula>
     </cfRule>
@@ -7193,7 +7291,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F170" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F5:F171" type="list">
       <formula1>"Nezahájeno,Rozpracováno,Hotovo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7226,24 +7324,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7332,7 +7430,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B8" s="6" t="n">
         <f aca="false">COUNTIF(Úkoly!$D$5:$D$37,A8)</f>
@@ -7353,7 +7451,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">SUM(B4:B8)</f>
@@ -7401,29 +7499,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>3</v>
@@ -7440,7 +7538,7 @@
     </row>
     <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B5" s="19" t="n">
         <v>46303</v>
@@ -7449,27 +7547,27 @@
         <v>46309</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="B6" s="22" t="n">
         <v>46310</v>
@@ -7479,24 +7577,24 @@
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="6" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="B7" s="22" t="n">
         <v>46317</v>
@@ -7506,24 +7604,24 @@
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="6" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="B8" s="22" t="n">
         <v>46324</v>
@@ -7533,24 +7631,24 @@
       </c>
       <c r="D8" s="14"/>
       <c r="E8" s="6" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="B9" s="22" t="n">
         <v>46331</v>
@@ -7559,27 +7657,27 @@
         <v>46337</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>46338</v>
@@ -7588,27 +7686,27 @@
         <v>46344</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="B11" s="22" t="n">
         <v>46345</v>
@@ -7618,24 +7716,24 @@
       </c>
       <c r="D11" s="14"/>
       <c r="E11" s="6" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>46352</v>
@@ -7644,27 +7742,27 @@
         <v>46358</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B13" s="24" t="n">
         <v>46359</v>
@@ -7673,27 +7771,27 @@
         <v>46365</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="B14" s="24" t="n">
         <v>46366</v>
@@ -7702,22 +7800,22 @@
         <v>46372</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7731,10 +7829,10 @@
         <v>46373</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
@@ -7752,10 +7850,10 @@
         <v>46393</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>V repu je jen požadavky + matice oprávnění; popis portálu (15_Webovy_portal_popis.docx) chybí – nahrát. Nesoulad: Ema dává pacientovi GET /alerty, matice portálu ne – sjednotit.</t>
+          <t>Popis portálu v Sabi/15_Webovy_portal_popis.docx. Oprávnění pacienta k alertům sladí Ema v API (viz Vzkazy).</t>
         </is>
       </c>
       <c r="H19" s="13">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G79" s="10" t="n"/>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F81" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G81" s="10" t="n"/>
@@ -4970,14 +4970,10 @@
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
-        </is>
-      </c>
-      <c r="G82" s="10" t="inlineStr">
-        <is>
-          <t>Popis portálu nahrát do repa.</t>
-        </is>
-      </c>
+          <t>Hotovo</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="n"/>
     </row>
     <row r="83" ht="42.75" customHeight="1">
       <c r="A83" s="15" t="n">

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2188,12 +2188,12 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Rozpracováno</t>
         </is>
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Podklady už existují: testy T01–T10 (Maky/04) a testovací scénáře API (Ema/Implementace §7).</t>
+          <t>Návrh v Sabi/17_Testovani.docx (~2,5 strany). Zbývá: scénáře A-, S- a I- odsouhlasit s Maky, Emou a rolí 4.</t>
         </is>
       </c>
       <c r="H21" s="13">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="F87" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G87" s="10" t="n"/>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G88" s="10" t="n"/>
@@ -5160,10 +5160,14 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G89" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Scénáře převzaty z Maky/04 a Ema/Implementace §7; integrátor navržen – ověřit.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n">
@@ -5186,7 +5190,7 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G90" s="10" t="n"/>
@@ -5212,7 +5216,7 @@
       </c>
       <c r="F91" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G91" s="10" t="n"/>
@@ -5238,7 +5242,7 @@
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G92" s="10" t="n"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Požadavky mají zatím jen role 1 (M-F01–10) a role 2 (FP-P01–11); role 3 a 4 chybí. Sjednotit prefixy (M-F vs FP-A), spojit do jedné tabulky, MoSCoW. Chybí: průvodce měřením, připomínky, nepravidelný rytmus, doporučení lékaře v aplikaci.</t>
+          <t>Spojeno do spolecny/Pozadavky_spolecne.xlsx (46 FP + 17 NFP, MoSCoW). Čeká na odsouhlasení vlastníky bloků do 1. 11., pak kapitola (Sabi).</t>
         </is>
       </c>
       <c r="H6" s="13">
@@ -3048,10 +3048,14 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="n"/>
+          <t>Hotovo</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Ve společné tabulce; čeká na potvrzení</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="28.5" customHeight="1">
       <c r="A12" s="15" t="n">
@@ -3074,10 +3078,14 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="n"/>
+          <t>Hotovo</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Ve společné tabulce; čeká na potvrzení</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28.5" customHeight="1">
       <c r="A13" s="15" t="n">
@@ -3100,10 +3108,14 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Očíslováno, MoSCoW navrženo – odsouhlasit</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2151,12 +2151,12 @@
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Rozpracováno</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Počkat na vzhled aplikace (Maky) – sjednotit barvy.</t>
+          <t>7 obrazovek v Sabi/GUI_portal + popis v Sabi/16_GUI_portal.docx, barvy podle návrhu Maky. Zbývá odsouhlasit s Maky (jednotný styl, barevné indikátory).</t>
         </is>
       </c>
       <c r="H20" s="13">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="F83" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G83" s="10" t="n"/>
@@ -5038,10 +5038,14 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G84" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>Barvy převzaty od Maky; sladit indikátory hodnot</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
@@ -5064,7 +5068,7 @@
       </c>
       <c r="F85" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G85" s="10" t="n"/>
@@ -5090,7 +5094,7 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G86" s="10" t="n"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Domi (možná převezme Sabi – upřesnit)</t>
+          <t>Sabi (převzala roli 4 od Domi 30. 10.) – výstupy v Role4-S</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Maky = 1, Sabi = 2, Ema = 3, Domi = 4</t>
+          <t>Maky = 1, Sabi = 2 i 4, Ema = 3</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Domi zatím nic; možná převezme Sabi – rozhodnout v týmu a promítnout do výkazu práce</t>
+          <t>Roli 4 dělá Sabi (od 30. 10.), výstupy ve složce Role4-S; promítnout do výkazu práce a říct cvičícím 12. 11.</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>Otevřené</t>
+          <t>Vyřešeno</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Role 4 – složka Domi je zatím prázdná.</t>
+          <t>Sabi (role 4). Posunuto z 28. 10. – potřeba na konzultaci 12. 11.</t>
         </is>
       </c>
       <c r="H27" s="13">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Rozpracováno</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Role 4 – podklad: tabulka NisSynchronizace v ER Emy.</t>
+          <t>Diagram (8 stavů) + popis v Role4-S. Zbývá: export PNG z draw.io a potvrdit s Emou hodnoty NisSynchronizace.stav (čeká / odesláno / chyba).</t>
         </is>
       </c>
       <c r="H28" s="13">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Role 4.</t>
+          <t>Sabi (role 4). Sladit s ER Emy (NisSynchronizace) a LOINC kódy.</t>
         </is>
       </c>
       <c r="H29" s="13">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Role 4 – termín 18.11.; zdroje ESH už jsou připravené (Sabi).</t>
+          <t>Sabi (role 4). Zdroje ESH už připravené.</t>
         </is>
       </c>
       <c r="H30" s="13">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Role 4.</t>
+          <t>Sabi (role 4) – případně nabídnout Emě (souvisí se serverem).</t>
         </is>
       </c>
       <c r="H31" s="13">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="F124" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G124" s="10" t="n"/>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="F125" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G125" s="10" t="n"/>
@@ -6186,10 +6186,14 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G126" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>Diagram + popis hotové, chybí export PNG</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="7" t="n">

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Rozpracováno</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Sabi (role 4). Posunuto z 28. 10. – potřeba na konzultaci 12. 11.</t>
+          <t>Diagram + popis v Role4-S (Administrátor 5 UC, NIS 4 UC, Časovač). Zbývá export PNG z draw.io.</t>
         </is>
       </c>
       <c r="H27" s="13">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>Diagram (8 stavů) + popis v Role4-S. Zbývá: export PNG z draw.io a potvrdit s Emou hodnoty NisSynchronizace.stav (čeká / odesláno / chyba).</t>
+          <t>Diagram, PNG (SD_synchronizace.drawio.png) a popis v Role4-S. Zbývá jen potvrdit s Emou hodnoty NisSynchronizace.stav (čeká / odesláno / chyba).</t>
         </is>
       </c>
       <c r="H28" s="13">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G120" s="10" t="n"/>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G121" s="10" t="n"/>
@@ -6078,10 +6078,14 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G122" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>Chybí export PNG</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n">
@@ -6104,7 +6108,7 @@
       </c>
       <c r="F123" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G123" s="10" t="n"/>
@@ -6186,14 +6190,10 @@
       </c>
       <c r="F126" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
-        </is>
-      </c>
-      <c r="G126" s="10" t="inlineStr">
-        <is>
-          <t>Diagram + popis hotové, chybí export PNG</t>
-        </is>
-      </c>
+          <t>Hotovo</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="7" t="n">

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2484,12 +2484,12 @@
       </c>
       <c r="F29" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Rozpracováno</t>
         </is>
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Sabi (role 4). Sladit s ER Emy (NisSynchronizace) a LOINC kódy.</t>
+          <t>Text v Role4-S/25_Integrator_FHIR.docx (mapování, průběh, nastavení, ukázka JSON). Zbývá: potvrdit s Emou NisSynchronizace a práva DB účtu; na konzultaci ověřit hloubku FHIR a FP-I09.</t>
         </is>
       </c>
       <c r="H29" s="13">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G127" s="10" t="n"/>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G128" s="10" t="n"/>
@@ -6272,10 +6272,14 @@
       </c>
       <c r="F129" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G129" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G129" s="10" t="inlineStr">
+        <is>
+          <t>Životospráva do NIS – otevřené (FP-I09)</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="28.5" customHeight="1">
       <c r="A130" s="7" t="n">
@@ -6298,7 +6302,7 @@
       </c>
       <c r="F130" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G130" s="10" t="n"/>
@@ -6324,7 +6328,7 @@
       </c>
       <c r="F131" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G131" s="10" t="n"/>
@@ -6350,7 +6354,7 @@
       </c>
       <c r="F132" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G132" s="10" t="n"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F27" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Diagram + popis v Role4-S (Administrátor 5 UC, NIS 4 UC, Časovač). Zbývá export PNG z draw.io.</t>
+          <t>Role4-S: UC_integrator_NIS.drawio + PNG + popis. Administrátor 5 UC, NIS 4 UC, Časovač.</t>
         </is>
       </c>
       <c r="H27" s="13">
@@ -6078,14 +6078,10 @@
       </c>
       <c r="F122" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
-        </is>
-      </c>
-      <c r="G122" s="10" t="inlineStr">
-        <is>
-          <t>Chybí export PNG</t>
-        </is>
-      </c>
+          <t>Hotovo</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n">

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -1596,12 +1596,12 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>Chybí krok 1.4 – zdůvodnění volby hypertenze do Úvodu (čeká na roli 4).</t>
+          <t>Zdůvodnění volby je v Úvodu (Role4-S/26_Uvod.docx).</t>
         </is>
       </c>
       <c r="H5" s="13">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Rozpracováno</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Sabi (role 4). Zdroje ESH už připravené.</t>
+          <t>Návrh v Role4-S/26_Uvod.docx (~2,5 str., 9 zdrojů). Zbývá: přečíst týmem, u [4] a [7] ověřit ročník/číslo v originále.</t>
         </is>
       </c>
       <c r="H30" s="13">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G8" s="10" t="n"/>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F133" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G133" s="10" t="n"/>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="F134" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G134" s="10" t="n"/>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G135" s="10" t="n"/>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F136" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G136" s="10" t="n"/>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="F137" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G137" s="10" t="n"/>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F138" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G138" s="10" t="n"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -1786,7 +1786,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Bezpečnost je rozepsaná v Ema/Implementace §4 a Maky NFR; chybí společná podkapitola a rozhodnutí o retenci dat (GDPR).</t>
+          <t>Návrh podkapitoly v spolecny/06_Bezpecnost_GDPR.docx (Sabi). Zbývá: odsouhlasit týmem, rozhodnout dobu uchování dat (NFP-16), každá role odkáže na podkapitolu ve svém bloku.</t>
         </is>
       </c>
       <c r="H10" s="13">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G31" s="10" t="n"/>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G32" s="10" t="n"/>
@@ -3655,7 +3655,11 @@
           <t>Rozpracováno</t>
         </is>
       </c>
-      <c r="G33" s="10" t="n"/>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Doba uchování – otevřené (NFP-16)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
@@ -3704,10 +3708,14 @@
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Podkapitola napsaná; odkazy v blocích doplní každá role</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="7" t="n">

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2558,12 +2558,12 @@
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Rozpracováno</t>
         </is>
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Sabi (role 4) – případně nabídnout Emě (souvisí se serverem).</t>
+          <t>Návrh v Role4-S/27_Nasazeni.docx + Deployment_diagram.drawio. Zbývá: export PNG, Ema ověří soulad s Implementací (technologie).</t>
         </is>
       </c>
       <c r="H31" s="13">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="F139" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G139" s="10" t="n"/>
@@ -6574,7 +6574,7 @@
       </c>
       <c r="F140" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G140" s="10" t="n"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="F141" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G141" s="10" t="n"/>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="F142" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G142" s="10" t="n"/>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G143" s="10" t="n"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -1675,7 +1675,7 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Aktéři jsou v UC diagramech, tok dat v Maky/02-architektura a komponenty v Maky/04. Chybí společné odsouhlasení a role 4.</t>
+          <t>spolecny/03_Akteri_a_rozhrani.docx: aktéři, matice aktér × část, tabulka rozhraní. Zbývá odsouhlasit v týmu.</t>
         </is>
       </c>
       <c r="H7" s="13">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G15" s="10" t="n"/>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G16" s="10" t="n"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Rozpracováno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G18" s="10" t="n"/>

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Spojeno do spolecny/Pozadavky_spolecne.xlsx (46 FP + 17 NFP, MoSCoW). Čeká na odsouhlasení vlastníky bloků do 1. 11., pak kapitola (Sabi).</t>
+          <t>Tabulka spolecny/Pozadavky_spolecne.xlsx (čeká na odsouhlasení do 1. 11.) + návrh kapitoly spolecny/02_Analyza_pozadavku.docx (persony, MoSCoW, příloha A). Po odsouhlasení přegenerovat přílohu.</t>
         </is>
       </c>
       <c r="H6" s="13">
@@ -3025,7 +3025,11 @@
           <t>Rozpracováno</t>
         </is>
       </c>
-      <c r="G10" s="10" t="n"/>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>3 persony v kapitole – odsouhlasit</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="42.75" customHeight="1">
       <c r="A11" s="15" t="n">
@@ -3138,10 +3142,14 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Návrh kapitoly hotový; čeká na odsouhlasení požadavků</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="7" t="n">

--- a/Rozdeleni_projektu_SI2.xlsx
+++ b/Rozdeleni_projektu_SI2.xlsx
@@ -2595,10 +2595,14 @@
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G32" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Návrh v spolecny/28_Zhodnoceni.docx (Sabi). Zbývá odsouhlasit v týmu a doladit po konzultaci.</t>
+        </is>
+      </c>
       <c r="H32" s="13">
         <f>COUNTIFS('Osnova kroků'!$A$5:$A$171,A32,'Osnova kroků'!$F$5:$F$171,"Hotovo")&amp;" / "&amp;COUNTIF('Osnova kroků'!$A$5:$A$171,A32)</f>
         <v/>
@@ -6690,7 +6694,7 @@
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G144" s="10" t="n"/>
@@ -6716,7 +6720,7 @@
       </c>
       <c r="F145" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G145" s="10" t="n"/>
@@ -6742,7 +6746,7 @@
       </c>
       <c r="F146" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
+          <t>Hotovo</t>
         </is>
       </c>
       <c r="G146" s="10" t="n"/>
@@ -6768,10 +6772,14 @@
       </c>
       <c r="F147" s="10" t="inlineStr">
         <is>
-          <t>Nezahájeno</t>
-        </is>
-      </c>
-      <c r="G147" s="10" t="n"/>
+          <t>Rozpracováno</t>
+        </is>
+      </c>
+      <c r="G147" s="10" t="inlineStr">
+        <is>
+          <t>Napsáno, čeká na odsouhlasení</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n">
